--- a/Lista_Grants_Mentoria.xlsx
+++ b/Lista_Grants_Mentoria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/NEXUS/2026/Dash_Nexus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1826" documentId="13_ncr:1_{54A37689-96D9-4BFE-9E28-8766A1F3212B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72AE95A2-F412-4AFB-AC3C-7F3CDE75F6E9}"/>
+  <xr:revisionPtr revIDLastSave="1827" documentId="13_ncr:1_{54A37689-96D9-4BFE-9E28-8766A1F3212B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833FD1C7-15FB-4B96-B8F3-4A7106B55349}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1933,13 +1933,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{443F3E09-02E4-44F3-8428-F05D0B7CD6E5}" name="Table1" displayName="Table1" ref="A1:M450" totalsRowShown="0">
-  <autoFilter ref="A1:M450" xr:uid="{443F3E09-02E4-44F3-8428-F05D0B7CD6E5}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="Sim"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M450" xr:uid="{443F3E09-02E4-44F3-8428-F05D0B7CD6E5}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{DC8E42B1-C5DD-4FD8-BA52-9804B814B2E7}" name="Distrito"/>
     <tableColumn id="2" xr3:uid="{1E34E00E-4C4B-410D-9D66-0B462945AB80}" name="Facilitadores"/>
@@ -5869,7 +5863,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -6249,7 +6243,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>97</v>
       </c>
@@ -16588,7 +16582,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="378" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>97</v>
       </c>
@@ -16620,7 +16614,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="379" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>97</v>
       </c>
@@ -16652,7 +16646,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="380" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>97</v>
       </c>
@@ -16684,7 +16678,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="381" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>97</v>
       </c>
@@ -16716,7 +16710,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="382" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>97</v>
       </c>
@@ -16748,7 +16742,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="383" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>97</v>
       </c>
@@ -16780,7 +16774,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="384" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>97</v>
       </c>
@@ -16812,7 +16806,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>97</v>
       </c>
@@ -16844,7 +16838,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>97</v>
       </c>
@@ -16876,7 +16870,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>97</v>
       </c>
@@ -16908,7 +16902,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>97</v>
       </c>
@@ -16940,7 +16934,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>97</v>
       </c>
@@ -16972,7 +16966,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>97</v>
       </c>
@@ -17004,7 +16998,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>97</v>
       </c>
@@ -17036,7 +17030,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>97</v>
       </c>
@@ -17068,7 +17062,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>97</v>
       </c>
@@ -17100,7 +17094,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>97</v>
       </c>
@@ -17132,7 +17126,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>97</v>
       </c>
@@ -17164,7 +17158,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>97</v>
       </c>
@@ -17196,7 +17190,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>97</v>
       </c>
@@ -17228,7 +17222,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>7</v>
       </c>
@@ -17260,7 +17254,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>7</v>
       </c>
@@ -17292,7 +17286,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>7</v>
       </c>
@@ -17324,7 +17318,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>7</v>
       </c>
@@ -17356,7 +17350,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>7</v>
       </c>
@@ -17388,7 +17382,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>7</v>
       </c>
@@ -17420,7 +17414,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>7</v>
       </c>
@@ -17452,7 +17446,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>7</v>
       </c>
@@ -17484,7 +17478,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>7</v>
       </c>
@@ -17516,7 +17510,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>7</v>
       </c>
@@ -17548,7 +17542,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>7</v>
       </c>
@@ -17580,7 +17574,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>7</v>
       </c>
@@ -17612,7 +17606,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>7</v>
       </c>
@@ -17644,7 +17638,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>7</v>
       </c>
@@ -17676,7 +17670,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>7</v>
       </c>
@@ -17708,7 +17702,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>7</v>
       </c>
@@ -17740,7 +17734,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>7</v>
       </c>
@@ -17772,7 +17766,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>7</v>
       </c>
@@ -17804,7 +17798,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>7</v>
       </c>
@@ -17836,7 +17830,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="417" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>7</v>
       </c>
@@ -17868,7 +17862,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="418" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>7</v>
       </c>
@@ -17900,7 +17894,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="419" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>7</v>
       </c>
@@ -17932,7 +17926,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="420" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>7</v>
       </c>
@@ -17964,7 +17958,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="421" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>7</v>
       </c>
@@ -17996,7 +17990,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="422" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>7</v>
       </c>
@@ -18028,7 +18022,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="423" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>7</v>
       </c>
@@ -18060,7 +18054,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="424" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>7</v>
       </c>
@@ -18092,7 +18086,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="425" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>7</v>
       </c>
@@ -18124,7 +18118,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="426" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>7</v>
       </c>
@@ -18194,7 +18188,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="428" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>7</v>
       </c>
@@ -18226,7 +18220,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="429" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>7</v>
       </c>
@@ -18258,7 +18252,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="430" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>7</v>
       </c>
@@ -18290,7 +18284,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="431" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>7</v>
       </c>
@@ -18322,7 +18316,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="432" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>7</v>
       </c>
@@ -18354,7 +18348,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>7</v>
       </c>
@@ -18386,7 +18380,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>7</v>
       </c>
@@ -18418,7 +18412,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>7</v>
       </c>
@@ -18450,7 +18444,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>7</v>
       </c>
@@ -18482,7 +18476,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>7</v>
       </c>
@@ -18514,7 +18508,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>7</v>
       </c>
@@ -18546,7 +18540,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>7</v>
       </c>
@@ -18578,7 +18572,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>7</v>
       </c>
@@ -18610,7 +18604,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>7</v>
       </c>
@@ -18642,7 +18636,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>7</v>
       </c>
@@ -18674,7 +18668,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>7</v>
       </c>
@@ -18706,7 +18700,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>7</v>
       </c>
@@ -18738,7 +18732,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>7</v>
       </c>
@@ -18770,7 +18764,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>7</v>
       </c>
@@ -18802,7 +18796,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>7</v>
       </c>
@@ -18834,7 +18828,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>7</v>
       </c>
@@ -18866,7 +18860,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>7</v>
       </c>
@@ -18898,7 +18892,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>7</v>
       </c>
@@ -18943,26 +18937,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -19197,26 +19171,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DD773D5-C77E-4BE7-B333-7D7BD35C149E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{740CB11B-765A-4E9B-962E-5A759873CC55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0309DC03-8AF9-4F10-8E38-DF287EC74A10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19233,4 +19208,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{740CB11B-765A-4E9B-962E-5A759873CC55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DD773D5-C77E-4BE7-B333-7D7BD35C149E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>